--- a/AAII_Financials/Quarterly/RELT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RELT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>RELT</t>
   </si>
@@ -656,171 +656,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3">
         <v>400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1000</v>
       </c>
       <c r="I8" s="3">
         <v>1000</v>
       </c>
       <c r="J8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>500</v>
       </c>
       <c r="R8" s="3">
         <v>500</v>
       </c>
       <c r="S8" s="3">
+        <v>500</v>
+      </c>
+      <c r="T8" s="3">
         <v>600</v>
-      </c>
-      <c r="T8" s="3">
-        <v>400</v>
       </c>
       <c r="U8" s="3">
         <v>400</v>
@@ -835,39 +839,42 @@
         <v>400</v>
       </c>
       <c r="Y8" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z8" s="3">
         <v>200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>900</v>
       </c>
       <c r="G9" s="3">
         <v>900</v>
       </c>
       <c r="H9" s="3">
+        <v>900</v>
+      </c>
+      <c r="I9" s="3">
         <v>700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>500</v>
       </c>
       <c r="L9" s="3">
         <v>500</v>
@@ -879,28 +886,28 @@
         <v>500</v>
       </c>
       <c r="O9" s="3">
+        <v>500</v>
+      </c>
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>300</v>
-      </c>
-      <c r="R9" s="3">
-        <v>400</v>
       </c>
       <c r="S9" s="3">
         <v>400</v>
       </c>
       <c r="T9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="U9" s="3">
         <v>200</v>
       </c>
       <c r="V9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W9" s="3">
         <v>300</v>
@@ -909,63 +916,66 @@
         <v>300</v>
       </c>
       <c r="Y9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z9" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
-      </c>
-      <c r="E10" s="3">
-        <v>300</v>
       </c>
       <c r="F10" s="3">
         <v>300</v>
       </c>
       <c r="G10" s="3">
+        <v>300</v>
+      </c>
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
       <c r="K10" s="3">
         <v>100</v>
       </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
       <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
-        <v>100</v>
-      </c>
       <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
-        <v>100</v>
-      </c>
       <c r="S10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>200</v>
@@ -974,7 +984,7 @@
         <v>200</v>
       </c>
       <c r="V10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
@@ -983,13 +993,16 @@
         <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1181,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1175,8 +1195,8 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1184,20 +1204,20 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1214,8 +1234,8 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1238,8 +1258,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,61 +1363,62 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>700</v>
       </c>
       <c r="L17" s="3">
         <v>700</v>
       </c>
       <c r="M17" s="3">
+        <v>700</v>
+      </c>
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>800</v>
-      </c>
-      <c r="R17" s="3">
-        <v>500</v>
       </c>
       <c r="S17" s="3">
         <v>500</v>
       </c>
       <c r="T17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="U17" s="3">
         <v>400</v>
@@ -1406,13 +1433,16 @@
         <v>400</v>
       </c>
       <c r="Y17" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z17" s="3">
         <v>200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1426,46 +1456,46 @@
         <v>0</v>
       </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>300</v>
       </c>
-      <c r="H18" s="3">
-        <v>100</v>
-      </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3">
         <v>-100</v>
       </c>
       <c r="L18" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M18" s="3">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
-        <v>100</v>
-      </c>
       <c r="O18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-300</v>
       </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
       <c r="S18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18" s="3">
         <v>0</v>
@@ -1485,8 +1515,11 @@
       <c r="Z18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1546,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1587,8 +1621,11 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1602,46 +1639,46 @@
         <v>0</v>
       </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
-        <v>100</v>
-      </c>
       <c r="I21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-100</v>
       </c>
       <c r="L21" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M21" s="3">
+        <v>100</v>
+      </c>
+      <c r="N21" s="3">
         <v>-400</v>
       </c>
-      <c r="N21" s="3">
-        <v>100</v>
-      </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3">
         <v>0</v>
       </c>
       <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
       <c r="S21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U21" s="3">
         <v>0</v>
@@ -1650,19 +1687,22 @@
         <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y21" s="3">
         <v>0</v>
       </c>
       <c r="Z21" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1732,64 +1772,67 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>200</v>
       </c>
-      <c r="H23" s="3">
-        <v>100</v>
-      </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
         <v>-100</v>
       </c>
       <c r="L23" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M23" s="3">
+        <v>100</v>
+      </c>
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
-        <v>100</v>
-      </c>
       <c r="O23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23" s="3">
         <v>0</v>
       </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U23" s="3">
         <v>0</v>
@@ -1798,19 +1841,22 @@
         <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y23" s="3">
         <v>0</v>
       </c>
       <c r="Z23" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1829,12 +1875,12 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1883,8 +1929,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,61 +2006,64 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>200</v>
       </c>
-      <c r="H26" s="3">
-        <v>100</v>
-      </c>
       <c r="I26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
         <v>-100</v>
       </c>
       <c r="L26" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M26" s="3">
+        <v>100</v>
+      </c>
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
-        <v>100</v>
-      </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3">
         <v>0</v>
       </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
       <c r="S26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U26" s="3">
         <v>0</v>
@@ -2020,72 +2072,75 @@
         <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y26" s="3">
         <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
         <v>0</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>200</v>
       </c>
-      <c r="H27" s="3">
-        <v>100</v>
-      </c>
       <c r="I27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>-100</v>
       </c>
       <c r="L27" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M27" s="3">
+        <v>100</v>
+      </c>
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
-        <v>100</v>
-      </c>
       <c r="O27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27" s="3">
         <v>0</v>
       </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
       <c r="S27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U27" s="3">
         <v>0</v>
@@ -2094,19 +2149,22 @@
         <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y27" s="3">
         <v>0</v>
       </c>
       <c r="Z27" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2468,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2475,61 +2545,64 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
         <v>0</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>200</v>
       </c>
-      <c r="H33" s="3">
-        <v>100</v>
-      </c>
       <c r="I33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
         <v>-100</v>
       </c>
       <c r="L33" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M33" s="3">
+        <v>100</v>
+      </c>
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
-        <v>100</v>
-      </c>
       <c r="O33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33" s="3">
         <v>0</v>
       </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
       <c r="S33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U33" s="3">
         <v>0</v>
@@ -2538,19 +2611,22 @@
         <v>0</v>
       </c>
       <c r="W33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y33" s="3">
         <v>0</v>
       </c>
       <c r="Z33" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,61 +2699,64 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
         <v>0</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>200</v>
       </c>
-      <c r="H35" s="3">
-        <v>100</v>
-      </c>
       <c r="I35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
         <v>-100</v>
       </c>
       <c r="L35" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M35" s="3">
+        <v>100</v>
+      </c>
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
-        <v>100</v>
-      </c>
       <c r="O35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3">
         <v>0</v>
       </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
       <c r="S35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U35" s="3">
         <v>0</v>
@@ -2686,98 +2765,104 @@
         <v>0</v>
       </c>
       <c r="W35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y35" s="3">
         <v>0</v>
       </c>
       <c r="Z35" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,25 +2918,26 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E41" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>300</v>
       </c>
       <c r="G41" s="3">
+        <v>300</v>
+      </c>
+      <c r="H41" s="3">
         <v>500</v>
-      </c>
-      <c r="H41" s="3">
-        <v>300</v>
       </c>
       <c r="I41" s="3">
         <v>300</v>
@@ -2868,13 +2955,13 @@
         <v>300</v>
       </c>
       <c r="N41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O41" s="3">
         <v>200</v>
       </c>
       <c r="P41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q41" s="3">
         <v>300</v>
@@ -2883,7 +2970,7 @@
         <v>300</v>
       </c>
       <c r="S41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T41" s="3">
         <v>200</v>
@@ -2901,13 +2988,16 @@
         <v>200</v>
       </c>
       <c r="Y41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,8 +3070,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3016,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3054,8 +3147,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3066,19 +3162,19 @@
         <v>400</v>
       </c>
       <c r="F44" s="3">
+        <v>400</v>
+      </c>
+      <c r="G44" s="3">
         <v>300</v>
-      </c>
-      <c r="G44" s="3">
-        <v>200</v>
       </c>
       <c r="H44" s="3">
         <v>200</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3122,14 +3218,17 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-      <c r="Y44" s="3" t="s">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3157,8 +3256,8 @@
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
+      <c r="L45" s="3">
+        <v>0</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
@@ -3172,8 +3271,8 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -3190,8 +3289,8 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
+      <c r="W45" s="3">
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
@@ -3202,16 +3301,19 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>700</v>
+      </c>
+      <c r="E46" s="3">
         <v>500</v>
-      </c>
-      <c r="E46" s="3">
-        <v>700</v>
       </c>
       <c r="F46" s="3">
         <v>700</v>
@@ -3220,34 +3322,34 @@
         <v>700</v>
       </c>
       <c r="H46" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I46" s="3">
         <v>500</v>
       </c>
       <c r="J46" s="3">
+        <v>500</v>
+      </c>
+      <c r="K46" s="3">
         <v>400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>300</v>
-      </c>
-      <c r="L46" s="3">
-        <v>400</v>
       </c>
       <c r="M46" s="3">
         <v>400</v>
       </c>
       <c r="N46" s="3">
+        <v>400</v>
+      </c>
+      <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>400</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>300</v>
       </c>
       <c r="R46" s="3">
         <v>300</v>
@@ -3256,7 +3358,7 @@
         <v>300</v>
       </c>
       <c r="T46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U46" s="3">
         <v>200</v>
@@ -3271,13 +3373,16 @@
         <v>200</v>
       </c>
       <c r="Y46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3350,13 +3455,16 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -3377,7 +3485,7 @@
         <v>100</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -3395,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -3424,8 +3532,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,8 +3763,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,16 +3917,19 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>700</v>
+      </c>
+      <c r="E54" s="3">
         <v>500</v>
-      </c>
-      <c r="E54" s="3">
-        <v>800</v>
       </c>
       <c r="F54" s="3">
         <v>800</v>
@@ -3812,16 +3938,16 @@
         <v>800</v>
       </c>
       <c r="H54" s="3">
+        <v>800</v>
+      </c>
+      <c r="I54" s="3">
         <v>600</v>
-      </c>
-      <c r="I54" s="3">
-        <v>500</v>
       </c>
       <c r="J54" s="3">
         <v>500</v>
       </c>
       <c r="K54" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L54" s="3">
         <v>400</v>
@@ -3830,16 +3956,16 @@
         <v>400</v>
       </c>
       <c r="N54" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O54" s="3">
         <v>300</v>
       </c>
       <c r="P54" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q54" s="3">
         <v>400</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>300</v>
       </c>
       <c r="R54" s="3">
         <v>300</v>
@@ -3848,7 +3974,7 @@
         <v>300</v>
       </c>
       <c r="T54" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U54" s="3">
         <v>200</v>
@@ -3863,13 +3989,16 @@
         <v>200</v>
       </c>
       <c r="Y54" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z54" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,16 +4054,17 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -3963,16 +4094,16 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
-      </c>
-      <c r="P57" s="3">
-        <v>400</v>
       </c>
       <c r="Q57" s="3">
         <v>400</v>
       </c>
       <c r="R57" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
@@ -3996,10 +4127,13 @@
         <v>100</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4007,19 +4141,19 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
+        <v>200</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
-        <v>100</v>
-      </c>
       <c r="H58" s="3">
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4040,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4072,34 +4206,37 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
       </c>
       <c r="J59" s="3">
         <v>600</v>
       </c>
       <c r="K59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="L59" s="3">
         <v>400</v>
@@ -4108,17 +4245,17 @@
         <v>400</v>
       </c>
       <c r="N59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O59" s="3">
         <v>300</v>
       </c>
       <c r="P59" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3">
-        <v>100</v>
-      </c>
       <c r="R59" s="3">
         <v>100</v>
       </c>
@@ -4144,18 +4281,21 @@
         <v>100</v>
       </c>
       <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="3">
         <v>400</v>
-      </c>
-      <c r="E60" s="3">
-        <v>600</v>
       </c>
       <c r="F60" s="3">
         <v>600</v>
@@ -4164,7 +4304,7 @@
         <v>600</v>
       </c>
       <c r="H60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I60" s="3">
         <v>700</v>
@@ -4173,28 +4313,28 @@
         <v>700</v>
       </c>
       <c r="K60" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="L60" s="3">
         <v>500</v>
       </c>
       <c r="M60" s="3">
+        <v>500</v>
+      </c>
+      <c r="N60" s="3">
         <v>600</v>
-      </c>
-      <c r="N60" s="3">
-        <v>400</v>
       </c>
       <c r="O60" s="3">
         <v>400</v>
       </c>
       <c r="P60" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
-      </c>
-      <c r="R60" s="3">
-        <v>200</v>
       </c>
       <c r="S60" s="3">
         <v>200</v>
@@ -4203,10 +4343,10 @@
         <v>200</v>
       </c>
       <c r="U60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>200</v>
@@ -4218,10 +4358,13 @@
         <v>200</v>
       </c>
       <c r="Z60" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4253,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>100</v>
@@ -4262,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4294,8 +4437,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,55 +4745,58 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>600</v>
+      </c>
+      <c r="E66" s="3">
         <v>400</v>
-      </c>
-      <c r="E66" s="3">
-        <v>600</v>
       </c>
       <c r="F66" s="3">
         <v>600</v>
       </c>
       <c r="G66" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H66" s="3">
         <v>700</v>
       </c>
       <c r="I66" s="3">
+        <v>700</v>
+      </c>
+      <c r="J66" s="3">
         <v>800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>700</v>
-      </c>
-      <c r="K66" s="3">
-        <v>500</v>
       </c>
       <c r="L66" s="3">
         <v>500</v>
       </c>
       <c r="M66" s="3">
+        <v>500</v>
+      </c>
+      <c r="N66" s="3">
         <v>600</v>
-      </c>
-      <c r="N66" s="3">
-        <v>500</v>
       </c>
       <c r="O66" s="3">
         <v>500</v>
       </c>
       <c r="P66" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>500</v>
-      </c>
-      <c r="R66" s="3">
-        <v>200</v>
       </c>
       <c r="S66" s="3">
         <v>200</v>
@@ -4647,10 +4805,10 @@
         <v>200</v>
       </c>
       <c r="U66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V66" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W66" s="3">
         <v>200</v>
@@ -4662,10 +4820,13 @@
         <v>200</v>
       </c>
       <c r="Z66" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,13 +5159,16 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E72" s="3">
         <v>-300</v>
@@ -5006,43 +5180,43 @@
         <v>-300</v>
       </c>
       <c r="H72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I72" s="3">
         <v>-500</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-600</v>
       </c>
       <c r="J72" s="3">
         <v>-600</v>
       </c>
       <c r="K72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="L72" s="3">
         <v>-500</v>
       </c>
       <c r="M72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N72" s="3">
         <v>-600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-200</v>
-      </c>
-      <c r="O72" s="3">
-        <v>-300</v>
       </c>
       <c r="P72" s="3">
         <v>-300</v>
       </c>
       <c r="Q72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="R72" s="3">
-        <v>100</v>
-      </c>
       <c r="S72" s="3">
         <v>100</v>
       </c>
       <c r="T72" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
@@ -5054,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="X72" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="3">
         <v>-100</v>
@@ -5062,8 +5236,11 @@
       <c r="Z72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,8 +5467,11 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5293,37 +5479,37 @@
         <v>100</v>
       </c>
       <c r="E76" s="3">
+        <v>100</v>
+      </c>
+      <c r="F76" s="3">
         <v>200</v>
       </c>
-      <c r="F76" s="3">
-        <v>100</v>
-      </c>
       <c r="G76" s="3">
         <v>100</v>
       </c>
       <c r="H76" s="3">
+        <v>100</v>
+      </c>
+      <c r="I76" s="3">
         <v>-100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>-200</v>
       </c>
       <c r="J76" s="3">
         <v>-200</v>
       </c>
       <c r="K76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="L76" s="3">
         <v>-100</v>
       </c>
       <c r="M76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N76" s="3">
         <v>-200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-100</v>
-      </c>
-      <c r="O76" s="3">
-        <v>-200</v>
       </c>
       <c r="P76" s="3">
         <v>-200</v>
@@ -5332,11 +5518,11 @@
         <v>-200</v>
       </c>
       <c r="R76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S76" s="3">
         <v>200</v>
       </c>
-      <c r="S76" s="3">
-        <v>100</v>
-      </c>
       <c r="T76" s="3">
         <v>100</v>
       </c>
@@ -5350,7 +5536,7 @@
         <v>100</v>
       </c>
       <c r="X76" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y76" s="3">
         <v>0</v>
@@ -5358,8 +5544,11 @@
       <c r="Z76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,140 +5621,146 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
         <v>0</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>200</v>
       </c>
-      <c r="H81" s="3">
-        <v>100</v>
-      </c>
       <c r="I81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
         <v>-100</v>
       </c>
       <c r="L81" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="M81" s="3">
+        <v>100</v>
+      </c>
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
-        <v>100</v>
-      </c>
       <c r="O81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P81" s="3">
         <v>0</v>
       </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
       <c r="S81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U81" s="3">
         <v>0</v>
@@ -5574,19 +5769,22 @@
         <v>0</v>
       </c>
       <c r="W81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y81" s="3">
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5811,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,50 +6271,53 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
       <c r="M89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
@@ -6108,10 +6325,10 @@
         <v>0</v>
       </c>
       <c r="S89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -6120,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="W89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X89" s="3">
         <v>100</v>
@@ -6129,10 +6346,13 @@
         <v>100</v>
       </c>
       <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6206,8 +6427,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>8</v>
@@ -6224,8 +6445,8 @@
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6233,8 +6454,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6608,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6404,8 +6634,8 @@
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6428,8 +6658,8 @@
       <c r="Q94" s="3">
         <v>0</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>8</v>
@@ -6446,8 +6676,8 @@
       <c r="W94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6455,8 +6685,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7022,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6791,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
@@ -6853,8 +7099,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6927,50 +7176,53 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
         <v>0</v>
       </c>
@@ -6990,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="W102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X102" s="3">
         <v>100</v>
@@ -6999,6 +7251,9 @@
         <v>100</v>
       </c>
       <c r="Z102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RELT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RELT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>RELT</t>
   </si>
@@ -656,122 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -779,28 +786,28 @@
         <v>600</v>
       </c>
       <c r="E8" s="3">
+        <v>700</v>
+      </c>
+      <c r="F8" s="3">
+        <v>600</v>
+      </c>
+      <c r="G8" s="3">
         <v>400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>800</v>
-      </c>
-      <c r="L8" s="3">
-        <v>600</v>
       </c>
       <c r="M8" s="3">
         <v>800</v>
@@ -815,22 +822,22 @@
         <v>600</v>
       </c>
       <c r="Q8" s="3">
+        <v>800</v>
+      </c>
+      <c r="R8" s="3">
+        <v>600</v>
+      </c>
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>600</v>
-      </c>
-      <c r="U8" s="3">
-        <v>400</v>
-      </c>
-      <c r="V8" s="3">
-        <v>400</v>
       </c>
       <c r="W8" s="3">
         <v>400</v>
@@ -842,45 +849,51 @@
         <v>400</v>
       </c>
       <c r="Z8" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB8" s="3">
         <v>200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3">
         <v>500</v>
       </c>
       <c r="G9" s="3">
+        <v>200</v>
+      </c>
+      <c r="H9" s="3">
+        <v>500</v>
+      </c>
+      <c r="I9" s="3">
         <v>900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>900</v>
-      </c>
-      <c r="I9" s="3">
-        <v>700</v>
-      </c>
-      <c r="J9" s="3">
-        <v>800</v>
       </c>
       <c r="K9" s="3">
         <v>700</v>
       </c>
       <c r="L9" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="M9" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="N9" s="3">
         <v>500</v>
@@ -889,75 +902,81 @@
         <v>500</v>
       </c>
       <c r="P9" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>500</v>
+      </c>
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>200</v>
-      </c>
-      <c r="W9" s="3">
-        <v>300</v>
-      </c>
-      <c r="X9" s="3">
-        <v>300</v>
       </c>
       <c r="Y9" s="3">
         <v>300</v>
       </c>
       <c r="Z9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB9" s="3">
         <v>200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>500</v>
       </c>
       <c r="I10" s="3">
         <v>300</v>
       </c>
       <c r="J10" s="3">
+        <v>500</v>
+      </c>
+      <c r="K10" s="3">
+        <v>300</v>
+      </c>
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
       <c r="M10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
@@ -966,10 +985,10 @@
         <v>300</v>
       </c>
       <c r="P10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R10" s="3">
         <v>200</v>
@@ -981,28 +1000,34 @@
         <v>200</v>
       </c>
       <c r="U10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
       </c>
       <c r="W10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1217,14 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1198,32 +1237,32 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-100</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1237,11 +1276,11 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1261,8 +1300,14 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1338,8 +1383,14 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,67 +1415,69 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400</v>
+      </c>
+      <c r="E17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
+        <v>600</v>
+      </c>
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1000</v>
       </c>
       <c r="K17" s="3">
         <v>900</v>
       </c>
       <c r="L17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M17" s="3">
+        <v>900</v>
+      </c>
+      <c r="N17" s="3">
         <v>700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1000</v>
       </c>
       <c r="O17" s="3">
         <v>700</v>
       </c>
       <c r="P17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>700</v>
+      </c>
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>500</v>
-      </c>
-      <c r="U17" s="3">
-        <v>400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>400</v>
       </c>
       <c r="W17" s="3">
         <v>400</v>
@@ -1436,21 +1489,27 @@
         <v>400</v>
       </c>
       <c r="Z17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB17" s="3">
         <v>200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="3">
         <v>0</v>
@@ -1459,49 +1518,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
-        <v>100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
       <c r="K18" s="3">
+        <v>100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
-        <v>100</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
+        <v>100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
-        <v>100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3">
+        <v>100</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3">
-        <v>100</v>
-      </c>
       <c r="U18" s="3">
         <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W18" s="3">
         <v>0</v>
@@ -1518,8 +1577,14 @@
       <c r="AA18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,8 +1612,10 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1624,16 +1691,22 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -1642,67 +1715,73 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
-        <v>100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
+        <v>100</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
         <v>-100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="M21" s="3">
-        <v>100</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
+        <v>100</v>
+      </c>
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3">
-        <v>100</v>
-      </c>
       <c r="U21" s="3">
         <v>0</v>
       </c>
       <c r="V21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W21" s="3">
         <v>0</v>
       </c>
       <c r="X21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
         <v>0</v>
       </c>
       <c r="Z21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA21" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1775,88 +1854,100 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23" s="3">
+        <v>100</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
         <v>200</v>
       </c>
-      <c r="I23" s="3">
-        <v>100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>100</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
-        <v>100</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
+        <v>100</v>
+      </c>
+      <c r="P23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
-        <v>100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3">
-        <v>100</v>
-      </c>
       <c r="U23" s="3">
         <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W23" s="3">
         <v>0</v>
       </c>
       <c r="X23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="3">
         <v>0</v>
       </c>
       <c r="Z23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1878,15 +1969,15 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1932,8 +2023,14 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
+        <v>100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
-        <v>100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
-        <v>100</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
+        <v>100</v>
+      </c>
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
-        <v>100</v>
-      </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3">
-        <v>100</v>
-      </c>
       <c r="U26" s="3">
         <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W26" s="3">
         <v>0</v>
       </c>
       <c r="X26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="3">
         <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA26" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
+        <v>100</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
-        <v>100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>100</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
-        <v>100</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
+        <v>100</v>
+      </c>
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
-        <v>100</v>
-      </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3">
-        <v>100</v>
-      </c>
       <c r="U27" s="3">
         <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W27" s="3">
         <v>0</v>
       </c>
       <c r="X27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="3">
         <v>0</v>
       </c>
       <c r="Z27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,8 +2604,14 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2548,85 +2687,97 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
+        <v>100</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
-        <v>100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>100</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
-        <v>100</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
+        <v>100</v>
+      </c>
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
-        <v>100</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3">
-        <v>100</v>
-      </c>
       <c r="U33" s="3">
         <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W33" s="3">
         <v>0</v>
       </c>
       <c r="X33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="3">
         <v>0</v>
       </c>
       <c r="Z33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA33" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
+        <v>100</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
-        <v>100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>100</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
-        <v>100</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
+        <v>100</v>
+      </c>
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
-        <v>100</v>
-      </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3">
-        <v>100</v>
-      </c>
       <c r="U35" s="3">
         <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W35" s="3">
         <v>0</v>
       </c>
       <c r="X35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3">
         <v>0</v>
       </c>
       <c r="Z35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA35" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,8 +3090,10 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2928,22 +3101,22 @@
         <v>200</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
-      </c>
-      <c r="G41" s="3">
-        <v>300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>500</v>
       </c>
       <c r="I41" s="3">
         <v>300</v>
       </c>
       <c r="J41" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K41" s="3">
         <v>300</v>
@@ -2958,25 +3131,25 @@
         <v>300</v>
       </c>
       <c r="O41" s="3">
+        <v>300</v>
+      </c>
+      <c r="P41" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q41" s="3">
         <v>200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>200</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>300</v>
-      </c>
-      <c r="R41" s="3">
-        <v>300</v>
       </c>
       <c r="S41" s="3">
         <v>300</v>
       </c>
       <c r="T41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V41" s="3">
         <v>200</v>
@@ -2991,13 +3164,19 @@
         <v>200</v>
       </c>
       <c r="Z41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,8 +3252,14 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3112,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3124,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -3150,13 +3335,19 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>400</v>
@@ -3165,22 +3356,22 @@
         <v>400</v>
       </c>
       <c r="G44" s="3">
+        <v>400</v>
+      </c>
+      <c r="H44" s="3">
+        <v>400</v>
+      </c>
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
-        <v>100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3221,19 +3412,25 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-      <c r="Z44" s="3" t="s">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -3259,11 +3456,11 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
+        <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
@@ -3274,11 +3471,11 @@
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
@@ -3292,11 +3489,11 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
@@ -3304,8 +3501,14 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3313,58 +3516,58 @@
         <v>700</v>
       </c>
       <c r="E46" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="F46" s="3">
         <v>700</v>
       </c>
       <c r="G46" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H46" s="3">
         <v>700</v>
       </c>
       <c r="I46" s="3">
+        <v>700</v>
+      </c>
+      <c r="J46" s="3">
+        <v>700</v>
+      </c>
+      <c r="K46" s="3">
         <v>500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>500</v>
-      </c>
-      <c r="K46" s="3">
-        <v>400</v>
-      </c>
-      <c r="L46" s="3">
-        <v>300</v>
       </c>
       <c r="M46" s="3">
         <v>400</v>
       </c>
       <c r="N46" s="3">
+        <v>300</v>
+      </c>
+      <c r="O46" s="3">
         <v>400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>400</v>
-      </c>
-      <c r="R46" s="3">
-        <v>300</v>
-      </c>
-      <c r="S46" s="3">
-        <v>300</v>
       </c>
       <c r="T46" s="3">
         <v>300</v>
       </c>
       <c r="U46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W46" s="3">
         <v>200</v>
@@ -3376,13 +3579,19 @@
         <v>200</v>
       </c>
       <c r="Z46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB46" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3458,19 +3667,25 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
@@ -3488,10 +3703,10 @@
         <v>100</v>
       </c>
       <c r="L48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3506,13 +3721,13 @@
         <v>0</v>
       </c>
       <c r="R48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
       </c>
       <c r="T48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -3535,8 +3750,14 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3612,8 +3833,14 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,8 +3999,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3843,8 +4082,14 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,67 +4165,73 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>900</v>
+      </c>
+      <c r="F54" s="3">
         <v>700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>500</v>
-      </c>
-      <c r="F54" s="3">
-        <v>800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>800</v>
       </c>
       <c r="H54" s="3">
         <v>800</v>
       </c>
       <c r="I54" s="3">
+        <v>800</v>
+      </c>
+      <c r="J54" s="3">
+        <v>800</v>
+      </c>
+      <c r="K54" s="3">
         <v>600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>500</v>
-      </c>
-      <c r="L54" s="3">
-        <v>400</v>
-      </c>
-      <c r="M54" s="3">
-        <v>400</v>
       </c>
       <c r="N54" s="3">
         <v>400</v>
       </c>
       <c r="O54" s="3">
+        <v>400</v>
+      </c>
+      <c r="P54" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q54" s="3">
         <v>300</v>
-      </c>
-      <c r="P54" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>400</v>
       </c>
       <c r="R54" s="3">
         <v>300</v>
       </c>
       <c r="S54" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T54" s="3">
         <v>300</v>
       </c>
       <c r="U54" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V54" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W54" s="3">
         <v>200</v>
@@ -3992,13 +4243,19 @@
         <v>200</v>
       </c>
       <c r="Z54" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA54" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,8 +4314,10 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4064,13 +4325,13 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
@@ -4097,20 +4358,20 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>100</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="S57" s="3">
-        <v>100</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
-      </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
@@ -4130,10 +4391,16 @@
         <v>100</v>
       </c>
       <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4144,22 +4411,22 @@
         <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4177,13 +4444,13 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -4209,59 +4476,65 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
-        <v>100</v>
-      </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
         <v>500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>400</v>
       </c>
       <c r="N59" s="3">
         <v>400</v>
       </c>
       <c r="O59" s="3">
+        <v>400</v>
+      </c>
+      <c r="P59" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>100</v>
-      </c>
       <c r="T59" s="3">
         <v>100</v>
       </c>
@@ -4284,75 +4557,81 @@
         <v>100</v>
       </c>
       <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>500</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
-      </c>
-      <c r="E60" s="3">
-        <v>400</v>
       </c>
       <c r="F60" s="3">
         <v>600</v>
       </c>
       <c r="G60" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H60" s="3">
         <v>600</v>
       </c>
       <c r="I60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K60" s="3">
         <v>700</v>
       </c>
       <c r="L60" s="3">
+        <v>700</v>
+      </c>
+      <c r="M60" s="3">
+        <v>700</v>
+      </c>
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
-      </c>
-      <c r="S60" s="3">
-        <v>200</v>
-      </c>
-      <c r="T60" s="3">
-        <v>200</v>
       </c>
       <c r="U60" s="3">
         <v>200</v>
       </c>
       <c r="V60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W60" s="3">
         <v>200</v>
       </c>
       <c r="X60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y60" s="3">
         <v>200</v>
@@ -4361,18 +4640,24 @@
         <v>200</v>
       </c>
       <c r="AA60" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB60" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -4399,19 +4684,19 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4440,13 +4725,19 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -4517,8 +4808,14 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,73 +5057,79 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E66" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F66" s="3">
         <v>600</v>
       </c>
       <c r="G66" s="3">
+        <v>400</v>
+      </c>
+      <c r="H66" s="3">
         <v>600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>600</v>
+      </c>
+      <c r="J66" s="3">
         <v>700</v>
-      </c>
-      <c r="I66" s="3">
-        <v>700</v>
-      </c>
-      <c r="J66" s="3">
-        <v>800</v>
       </c>
       <c r="K66" s="3">
         <v>700</v>
       </c>
       <c r="L66" s="3">
+        <v>800</v>
+      </c>
+      <c r="M66" s="3">
+        <v>700</v>
+      </c>
+      <c r="N66" s="3">
         <v>500</v>
-      </c>
-      <c r="M66" s="3">
-        <v>500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>600</v>
       </c>
       <c r="O66" s="3">
         <v>500</v>
       </c>
       <c r="P66" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q66" s="3">
         <v>500</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>700</v>
       </c>
       <c r="R66" s="3">
         <v>500</v>
       </c>
       <c r="S66" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="T66" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="U66" s="3">
         <v>200</v>
       </c>
       <c r="V66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="W66" s="3">
         <v>200</v>
       </c>
       <c r="X66" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y66" s="3">
         <v>200</v>
@@ -4823,10 +5138,16 @@
         <v>200</v>
       </c>
       <c r="AA66" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AB66" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,19 +5503,25 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="E72" s="3">
         <v>-300</v>
       </c>
       <c r="F72" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G72" s="3">
         <v>-300</v>
@@ -5183,46 +5530,46 @@
         <v>-300</v>
       </c>
       <c r="I72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K72" s="3">
         <v>-500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3">
-        <v>100</v>
-      </c>
-      <c r="T72" s="3">
-        <v>100</v>
-      </c>
       <c r="U72" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V72" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -5231,16 +5578,22 @@
         <v>0</v>
       </c>
       <c r="Y72" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z72" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,43 +5835,49 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E76" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F76" s="3">
+        <v>100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>100</v>
+      </c>
+      <c r="H76" s="3">
         <v>200</v>
       </c>
-      <c r="G76" s="3">
-        <v>100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>100</v>
-      </c>
       <c r="I76" s="3">
+        <v>100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>100</v>
+      </c>
+      <c r="K76" s="3">
         <v>-100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-100</v>
-      </c>
-      <c r="M76" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N76" s="3">
-        <v>-200</v>
       </c>
       <c r="O76" s="3">
         <v>-100</v>
@@ -5515,20 +5886,20 @@
         <v>-200</v>
       </c>
       <c r="Q76" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="R76" s="3">
         <v>-200</v>
       </c>
       <c r="S76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U76" s="3">
         <v>200</v>
       </c>
-      <c r="T76" s="3">
-        <v>100</v>
-      </c>
-      <c r="U76" s="3">
-        <v>100</v>
-      </c>
       <c r="V76" s="3">
         <v>100</v>
       </c>
@@ -5539,16 +5910,22 @@
         <v>100</v>
       </c>
       <c r="Y76" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z76" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
+        <v>100</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
-        <v>100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>100</v>
+      </c>
+      <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
-        <v>100</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
+        <v>100</v>
+      </c>
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
-        <v>100</v>
-      </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3">
-        <v>100</v>
-      </c>
       <c r="U81" s="3">
         <v>0</v>
       </c>
       <c r="V81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W81" s="3">
         <v>0</v>
       </c>
       <c r="X81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="3">
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA81" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,8 +6207,10 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5889,8 +6286,14 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>200</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
       </c>
       <c r="G89" s="3">
         <v>-300</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J89" s="3">
         <v>200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>100</v>
-      </c>
       <c r="L89" s="3">
         <v>0</v>
       </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
       <c r="P89" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
       <c r="T89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
       </c>
       <c r="V89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
       <c r="X89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z89" s="3">
         <v>100</v>
       </c>
       <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6430,11 +6871,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
@@ -6448,17 +6889,23 @@
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,38 +7064,44 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -6661,11 +7120,11 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
@@ -6679,17 +7138,23 @@
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +7182,10 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6794,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,8 +7510,14 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7040,13 +7531,13 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -7102,8 +7593,14 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7179,56 +7676,62 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>100</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
         <v>0</v>
       </c>
@@ -7245,15 +7748,21 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z102" s="3">
         <v>100</v>
       </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RELT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RELT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>RELT</t>
   </si>
@@ -656,191 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1400</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1000</v>
       </c>
       <c r="L8" s="3">
         <v>1000</v>
       </c>
       <c r="M8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N8" s="3">
         <v>800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>300</v>
-      </c>
-      <c r="T8" s="3">
-        <v>500</v>
       </c>
       <c r="U8" s="3">
         <v>500</v>
       </c>
       <c r="V8" s="3">
+        <v>500</v>
+      </c>
+      <c r="W8" s="3">
         <v>600</v>
-      </c>
-      <c r="W8" s="3">
-        <v>400</v>
       </c>
       <c r="X8" s="3">
         <v>400</v>
@@ -855,48 +859,51 @@
         <v>400</v>
       </c>
       <c r="AB8" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC8" s="3">
         <v>200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>700</v>
+      </c>
+      <c r="E9" s="3">
         <v>300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>900</v>
       </c>
       <c r="J9" s="3">
         <v>900</v>
       </c>
       <c r="K9" s="3">
+        <v>900</v>
+      </c>
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
-      </c>
-      <c r="N9" s="3">
-        <v>500</v>
       </c>
       <c r="O9" s="3">
         <v>500</v>
@@ -908,28 +915,28 @@
         <v>500</v>
       </c>
       <c r="R9" s="3">
+        <v>500</v>
+      </c>
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>300</v>
-      </c>
-      <c r="U9" s="3">
-        <v>400</v>
       </c>
       <c r="V9" s="3">
         <v>400</v>
       </c>
       <c r="W9" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="X9" s="3">
         <v>200</v>
       </c>
       <c r="Y9" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z9" s="3">
         <v>300</v>
@@ -938,13 +945,16 @@
         <v>300</v>
       </c>
       <c r="AB9" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC9" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -955,55 +965,55 @@
         <v>300</v>
       </c>
       <c r="F10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>300</v>
       </c>
       <c r="I10" s="3">
         <v>300</v>
       </c>
       <c r="J10" s="3">
+        <v>300</v>
+      </c>
+      <c r="K10" s="3">
         <v>500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3">
-        <v>100</v>
-      </c>
       <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
-        <v>100</v>
-      </c>
       <c r="T10" s="3">
+        <v>100</v>
+      </c>
+      <c r="U10" s="3">
         <v>200</v>
       </c>
-      <c r="U10" s="3">
-        <v>100</v>
-      </c>
       <c r="V10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3">
         <v>200</v>
@@ -1012,7 +1022,7 @@
         <v>200</v>
       </c>
       <c r="Y10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Z10" s="3">
         <v>100</v>
@@ -1021,13 +1031,16 @@
         <v>100</v>
       </c>
       <c r="AB10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC10" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1243,8 +1263,8 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1252,20 +1272,20 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-100</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1282,8 +1302,8 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,70 +1443,71 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
         <v>400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>600</v>
       </c>
       <c r="F17" s="3">
         <v>600</v>
       </c>
       <c r="G17" s="3">
+        <v>600</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
-      </c>
-      <c r="N17" s="3">
-        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>700</v>
       </c>
       <c r="P17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
-      </c>
-      <c r="U17" s="3">
-        <v>500</v>
       </c>
       <c r="V17" s="3">
         <v>500</v>
       </c>
       <c r="W17" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="X17" s="3">
         <v>400</v>
@@ -1495,24 +1522,27 @@
         <v>400</v>
       </c>
       <c r="AB17" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC17" s="3">
         <v>200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
-        <v>100</v>
-      </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
@@ -1524,46 +1554,46 @@
         <v>0</v>
       </c>
       <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3">
-        <v>100</v>
-      </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3">
         <v>-100</v>
       </c>
       <c r="O18" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-400</v>
       </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
       <c r="R18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18" s="3">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
-        <v>0</v>
-      </c>
       <c r="V18" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X18" s="3">
         <v>0</v>
@@ -1583,8 +1613,11 @@
       <c r="AC18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1697,70 +1731,73 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
-        <v>100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>100</v>
-      </c>
       <c r="L21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
         <v>-100</v>
       </c>
       <c r="O21" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-400</v>
       </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
       <c r="R21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21" s="3">
         <v>0</v>
       </c>
       <c r="T21" s="3">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3">
         <v>-300</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
       <c r="V21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X21" s="3">
         <v>0</v>
@@ -1769,19 +1806,22 @@
         <v>0</v>
       </c>
       <c r="Z21" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB21" s="3">
         <v>0</v>
       </c>
       <c r="AC21" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1860,73 +1900,76 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E23" s="3">
         <v>100</v>
       </c>
       <c r="F23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
       <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
-        <v>100</v>
-      </c>
       <c r="L23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3">
         <v>-100</v>
       </c>
       <c r="O23" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-400</v>
       </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
       <c r="R23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23" s="3">
         <v>0</v>
       </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X23" s="3">
         <v>0</v>
@@ -1935,19 +1978,22 @@
         <v>0</v>
       </c>
       <c r="Z23" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB23" s="3">
         <v>0</v>
       </c>
       <c r="AC23" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1975,12 +2021,12 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -2029,8 +2075,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,70 +2161,73 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E26" s="3">
         <v>100</v>
       </c>
       <c r="F26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
       <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
       <c r="L26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3">
         <v>-100</v>
       </c>
       <c r="O26" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26" s="3">
         <v>0</v>
       </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-300</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X26" s="3">
         <v>0</v>
@@ -2184,81 +2236,84 @@
         <v>0</v>
       </c>
       <c r="Z26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB26" s="3">
         <v>0</v>
       </c>
       <c r="AC26" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E27" s="3">
         <v>100</v>
       </c>
       <c r="F27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
       <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
-        <v>100</v>
-      </c>
       <c r="L27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N27" s="3">
         <v>-100</v>
       </c>
       <c r="O27" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
       <c r="R27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27" s="3">
         <v>0</v>
       </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X27" s="3">
         <v>0</v>
@@ -2267,19 +2322,22 @@
         <v>0</v>
       </c>
       <c r="Z27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB27" s="3">
         <v>0</v>
       </c>
       <c r="AC27" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2693,70 +2763,73 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E33" s="3">
         <v>100</v>
       </c>
       <c r="F33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
       <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
-        <v>100</v>
-      </c>
       <c r="L33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3">
         <v>-100</v>
       </c>
       <c r="O33" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
       <c r="R33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33" s="3">
         <v>0</v>
       </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-300</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X33" s="3">
         <v>0</v>
@@ -2765,19 +2838,22 @@
         <v>0</v>
       </c>
       <c r="Z33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB33" s="3">
         <v>0</v>
       </c>
       <c r="AC33" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,70 +2935,73 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E35" s="3">
         <v>100</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
       <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
-        <v>100</v>
-      </c>
       <c r="L35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3">
         <v>-100</v>
       </c>
       <c r="O35" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
       <c r="R35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35" s="3">
         <v>0</v>
       </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-300</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X35" s="3">
         <v>0</v>
@@ -2931,107 +3010,113 @@
         <v>0</v>
       </c>
       <c r="Z35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB35" s="3">
         <v>0</v>
       </c>
       <c r="AC35" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,34 +3178,35 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I41" s="3">
         <v>300</v>
       </c>
       <c r="J41" s="3">
+        <v>300</v>
+      </c>
+      <c r="K41" s="3">
         <v>500</v>
-      </c>
-      <c r="K41" s="3">
-        <v>300</v>
       </c>
       <c r="L41" s="3">
         <v>300</v>
@@ -3137,13 +3224,13 @@
         <v>300</v>
       </c>
       <c r="Q41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R41" s="3">
         <v>200</v>
       </c>
       <c r="S41" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T41" s="3">
         <v>300</v>
@@ -3152,7 +3239,7 @@
         <v>300</v>
       </c>
       <c r="V41" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W41" s="3">
         <v>200</v>
@@ -3170,13 +3257,16 @@
         <v>200</v>
       </c>
       <c r="AB41" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,8 +3348,11 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3303,16 +3396,16 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3341,16 +3434,19 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
         <v>500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>400</v>
       </c>
       <c r="F44" s="3">
         <v>400</v>
@@ -3362,19 +3458,19 @@
         <v>400</v>
       </c>
       <c r="I44" s="3">
+        <v>400</v>
+      </c>
+      <c r="J44" s="3">
         <v>300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>200</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
       </c>
       <c r="L44" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3418,22 +3514,25 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-      <c r="AB44" s="3" t="s">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -3462,8 +3561,8 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
@@ -3477,8 +3576,8 @@
       <c r="S45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
+      <c r="T45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
@@ -3495,8 +3594,8 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
+      <c r="Z45" s="3">
+        <v>0</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
@@ -3507,25 +3606,28 @@
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>400</v>
+      </c>
+      <c r="E46" s="3">
         <v>700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>500</v>
-      </c>
-      <c r="H46" s="3">
-        <v>700</v>
       </c>
       <c r="I46" s="3">
         <v>700</v>
@@ -3534,34 +3636,34 @@
         <v>700</v>
       </c>
       <c r="K46" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="L46" s="3">
         <v>500</v>
       </c>
       <c r="M46" s="3">
+        <v>500</v>
+      </c>
+      <c r="N46" s="3">
         <v>400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
-      </c>
-      <c r="O46" s="3">
-        <v>400</v>
       </c>
       <c r="P46" s="3">
         <v>400</v>
       </c>
       <c r="Q46" s="3">
+        <v>400</v>
+      </c>
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>400</v>
-      </c>
-      <c r="T46" s="3">
-        <v>300</v>
       </c>
       <c r="U46" s="3">
         <v>300</v>
@@ -3570,7 +3672,7 @@
         <v>300</v>
       </c>
       <c r="W46" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X46" s="3">
         <v>200</v>
@@ -3585,13 +3687,16 @@
         <v>200</v>
       </c>
       <c r="AB46" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3673,8 +3778,11 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3685,10 +3793,10 @@
         <v>100</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
@@ -3709,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="N48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -3727,10 +3835,10 @@
         <v>0</v>
       </c>
       <c r="T48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3756,8 +3864,11 @@
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,8 +4122,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,25 +4294,28 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>500</v>
+      </c>
+      <c r="E54" s="3">
         <v>800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>500</v>
-      </c>
-      <c r="H54" s="3">
-        <v>800</v>
       </c>
       <c r="I54" s="3">
         <v>800</v>
@@ -4198,16 +4324,16 @@
         <v>800</v>
       </c>
       <c r="K54" s="3">
+        <v>800</v>
+      </c>
+      <c r="L54" s="3">
         <v>600</v>
-      </c>
-      <c r="L54" s="3">
-        <v>500</v>
       </c>
       <c r="M54" s="3">
         <v>500</v>
       </c>
       <c r="N54" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O54" s="3">
         <v>400</v>
@@ -4216,16 +4342,16 @@
         <v>400</v>
       </c>
       <c r="Q54" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R54" s="3">
         <v>300</v>
       </c>
       <c r="S54" s="3">
+        <v>300</v>
+      </c>
+      <c r="T54" s="3">
         <v>400</v>
-      </c>
-      <c r="T54" s="3">
-        <v>300</v>
       </c>
       <c r="U54" s="3">
         <v>300</v>
@@ -4234,7 +4360,7 @@
         <v>300</v>
       </c>
       <c r="W54" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="X54" s="3">
         <v>200</v>
@@ -4249,13 +4375,16 @@
         <v>200</v>
       </c>
       <c r="AB54" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC54" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,13 +4446,14 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
@@ -4331,10 +4462,10 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -4364,16 +4495,16 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
-      </c>
-      <c r="S57" s="3">
-        <v>400</v>
       </c>
       <c r="T57" s="3">
         <v>400</v>
       </c>
       <c r="U57" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
@@ -4397,15 +4528,18 @@
         <v>100</v>
       </c>
       <c r="AC57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>200</v>
@@ -4423,13 +4557,13 @@
         <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4450,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4491,34 +4628,34 @@
         <v>200</v>
       </c>
       <c r="E59" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F59" s="3">
         <v>300</v>
       </c>
       <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
-      </c>
-      <c r="I59" s="3">
-        <v>400</v>
       </c>
       <c r="J59" s="3">
         <v>400</v>
       </c>
       <c r="K59" s="3">
+        <v>400</v>
+      </c>
+      <c r="L59" s="3">
         <v>500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>600</v>
       </c>
       <c r="M59" s="3">
         <v>600</v>
       </c>
       <c r="N59" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="O59" s="3">
         <v>400</v>
@@ -4527,17 +4664,17 @@
         <v>400</v>
       </c>
       <c r="Q59" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R59" s="3">
         <v>300</v>
       </c>
       <c r="S59" s="3">
+        <v>300</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
-        <v>100</v>
-      </c>
       <c r="U59" s="3">
         <v>100</v>
       </c>
@@ -4563,27 +4700,30 @@
         <v>100</v>
       </c>
       <c r="AC59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>300</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
-      </c>
-      <c r="E60" s="3">
-        <v>600</v>
       </c>
       <c r="F60" s="3">
         <v>600</v>
       </c>
       <c r="G60" s="3">
+        <v>600</v>
+      </c>
+      <c r="H60" s="3">
         <v>400</v>
-      </c>
-      <c r="H60" s="3">
-        <v>600</v>
       </c>
       <c r="I60" s="3">
         <v>600</v>
@@ -4592,7 +4732,7 @@
         <v>600</v>
       </c>
       <c r="K60" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L60" s="3">
         <v>700</v>
@@ -4601,28 +4741,28 @@
         <v>700</v>
       </c>
       <c r="N60" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O60" s="3">
         <v>500</v>
       </c>
       <c r="P60" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q60" s="3">
         <v>600</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>400</v>
       </c>
       <c r="R60" s="3">
         <v>400</v>
       </c>
       <c r="S60" s="3">
+        <v>400</v>
+      </c>
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
-      </c>
-      <c r="U60" s="3">
-        <v>200</v>
       </c>
       <c r="V60" s="3">
         <v>200</v>
@@ -4631,10 +4771,10 @@
         <v>200</v>
       </c>
       <c r="X60" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y60" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>200</v>
@@ -4646,21 +4786,24 @@
         <v>200</v>
       </c>
       <c r="AC60" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AD60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -4690,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -4699,7 +4842,7 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4731,13 +4874,16 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,64 +5218,67 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>300</v>
+      </c>
+      <c r="E66" s="3">
         <v>500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>400</v>
-      </c>
-      <c r="H66" s="3">
-        <v>600</v>
       </c>
       <c r="I66" s="3">
         <v>600</v>
       </c>
       <c r="J66" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K66" s="3">
         <v>700</v>
       </c>
       <c r="L66" s="3">
+        <v>700</v>
+      </c>
+      <c r="M66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
-      </c>
-      <c r="N66" s="3">
-        <v>500</v>
       </c>
       <c r="O66" s="3">
         <v>500</v>
       </c>
       <c r="P66" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q66" s="3">
         <v>600</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>500</v>
       </c>
       <c r="R66" s="3">
         <v>500</v>
       </c>
       <c r="S66" s="3">
+        <v>500</v>
+      </c>
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>500</v>
-      </c>
-      <c r="U66" s="3">
-        <v>200</v>
       </c>
       <c r="V66" s="3">
         <v>200</v>
@@ -5129,10 +5287,10 @@
         <v>200</v>
       </c>
       <c r="X66" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y66" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z66" s="3">
         <v>200</v>
@@ -5144,10 +5302,13 @@
         <v>200</v>
       </c>
       <c r="AC66" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AD66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,22 +5680,25 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-400</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-300</v>
       </c>
       <c r="H72" s="3">
         <v>-300</v>
@@ -5536,43 +5710,43 @@
         <v>-300</v>
       </c>
       <c r="K72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L72" s="3">
         <v>-500</v>
-      </c>
-      <c r="L72" s="3">
-        <v>-600</v>
       </c>
       <c r="M72" s="3">
         <v>-600</v>
       </c>
       <c r="N72" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="O72" s="3">
         <v>-500</v>
       </c>
       <c r="P72" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-200</v>
-      </c>
-      <c r="R72" s="3">
-        <v>-300</v>
       </c>
       <c r="S72" s="3">
         <v>-300</v>
       </c>
       <c r="T72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="U72" s="3">
-        <v>100</v>
-      </c>
       <c r="V72" s="3">
         <v>100</v>
       </c>
       <c r="W72" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X72" s="3">
         <v>0</v>
@@ -5584,7 +5758,7 @@
         <v>0</v>
       </c>
       <c r="AA72" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB72" s="3">
         <v>-100</v>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,55 +6024,58 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>200</v>
+      </c>
+      <c r="E76" s="3">
         <v>300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>200</v>
       </c>
-      <c r="F76" s="3">
-        <v>100</v>
-      </c>
       <c r="G76" s="3">
         <v>100</v>
       </c>
       <c r="H76" s="3">
+        <v>100</v>
+      </c>
+      <c r="I76" s="3">
         <v>200</v>
       </c>
-      <c r="I76" s="3">
-        <v>100</v>
-      </c>
       <c r="J76" s="3">
         <v>100</v>
       </c>
       <c r="K76" s="3">
+        <v>100</v>
+      </c>
+      <c r="L76" s="3">
         <v>-100</v>
-      </c>
-      <c r="L76" s="3">
-        <v>-200</v>
       </c>
       <c r="M76" s="3">
         <v>-200</v>
       </c>
       <c r="N76" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="O76" s="3">
         <v>-100</v>
       </c>
       <c r="P76" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q76" s="3">
         <v>-200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-100</v>
-      </c>
-      <c r="R76" s="3">
-        <v>-200</v>
       </c>
       <c r="S76" s="3">
         <v>-200</v>
@@ -5898,11 +6084,11 @@
         <v>-200</v>
       </c>
       <c r="U76" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V76" s="3">
         <v>200</v>
       </c>
-      <c r="V76" s="3">
-        <v>100</v>
-      </c>
       <c r="W76" s="3">
         <v>100</v>
       </c>
@@ -5916,7 +6102,7 @@
         <v>100</v>
       </c>
       <c r="AA76" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB76" s="3">
         <v>0</v>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,158 +6196,164 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E81" s="3">
         <v>100</v>
       </c>
       <c r="F81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
       <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
-        <v>100</v>
-      </c>
       <c r="L81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N81" s="3">
         <v>-100</v>
       </c>
       <c r="O81" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="P81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
       <c r="R81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S81" s="3">
         <v>0</v>
       </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-300</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X81" s="3">
         <v>0</v>
@@ -6167,19 +6362,22 @@
         <v>0</v>
       </c>
       <c r="Z81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA81" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB81" s="3">
         <v>0</v>
       </c>
       <c r="AC81" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,59 +6921,62 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
-        <v>100</v>
-      </c>
       <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
       <c r="M89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
         <v>0</v>
       </c>
@@ -6767,10 +6984,10 @@
         <v>0</v>
       </c>
       <c r="V89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -6779,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA89" s="3">
         <v>100</v>
@@ -6788,10 +7005,13 @@
         <v>100</v>
       </c>
       <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6877,8 +7098,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
@@ -6895,8 +7116,8 @@
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7096,14 +7326,14 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -7126,8 +7356,8 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>8</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>8</v>
@@ -7144,8 +7374,8 @@
       <c r="Z94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,13 +7759,16 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -7537,10 +7783,10 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7682,59 +7931,62 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
         <v>0</v>
       </c>
@@ -7754,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3">
         <v>100</v>
@@ -7763,6 +8015,9 @@
         <v>100</v>
       </c>
       <c r="AC102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>
